--- a/data/trans_orig/IP74A2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP74A2_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto el alquiler en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos del alquiler en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>361</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>82,6%</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1149</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>546</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>87,76%</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>887</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12757</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21418</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
